--- a/business_forms/043_return_to_vendor_form--business_forms.xlsx
+++ b/business_forms/043_return_to_vendor_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>reason_for_return</t>
+          <t>return_reason</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>reason_for_return</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Reason for Return</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please explain the reason for return.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>request</t>
+          <t>customer_request</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer_request</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Customer Request</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Briefly describe the customer's request.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>reason_for_return</t>
+          <t>return_item_description</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>reason_for_return</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Return Item Description</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe the item being returned.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,7 +596,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>return_reason_type</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Return Reason Type</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select the reason for return.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,85 +628,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>return_item_description</t>
+          <t>return_item_quantity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>return_item_description</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Return Item Quantity</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter the quantity of items being returned.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>return_item_quantity</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>return_item_quantity</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Additional Notes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Is there anything else you'd like to add?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>reason_for_return</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>reason_for_return</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>reason_for_return</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>reason_for_return</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
         </is>
